--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-imagingstudy-radiology.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-imagingstudy-radiology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-dev</t>
+    <t>1.2.0a</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-imagingstudy-radiology.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-imagingstudy-radiology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0a</t>
+    <t>1.2.0-a-dev</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-imagingstudy-radiology.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-imagingstudy-radiology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-a-dev</t>
+    <t>1.2.0-a</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-imagingstudy-radiology.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-imagingstudy-radiology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-a-dev</t>
+    <t>1.2.0-release</t>
   </si>
   <si>
     <t>Name</t>
@@ -455,7 +455,7 @@
   </si>
   <si>
     <t>ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 {hasValue() or (children().count() &gt; id.count())}
-ext-1:拡張機能または値[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
+ext-1:extensionまたはvalue[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>ImagingStudy.modifierExtension</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-imagingstudy-radiology.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-imagingstudy-radiology.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-release</t>
+    <t>1.2.0-b</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-imagingstudy-radiology.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-imagingstudy-radiology.xlsx
@@ -1341,7 +1341,7 @@
     <t>パフォーマンスの種類</t>
   </si>
   <si>
-    <t>俳優のシリーズへの参加のタイプを区別する。</t>
+    <t>実施者・撮影者のシリーズへの参加のタイプを区別する。</t>
   </si>
   <si>
     <t>Allows disambiguation of the types of involvement of different performers.</t>
@@ -1363,7 +1363,7 @@
 </t>
   </si>
   <si>
-    <t>シリーズを演奏したのは誰ですか。</t>
+    <t>シリーズを実施・撮影したのは誰ですか。</t>
   </si>
   <si>
     <t>シリーズを行った人または物を示す。</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-imagingstudy-radiology.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-imagingstudy-radiology.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2154" uniqueCount="461">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2155" uniqueCount="462">
   <si>
     <t>Property</t>
   </si>
@@ -1227,7 +1227,10 @@
     <t>コードは、列挙型またはコードリストで、どの部位の検査なのかを示す。フリーではなく、DICOM定義書の中で示される語句（コード）をデフォルトとするが、JJ1017Pの小部位コードの利用を許容する。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ImagingStudy_Radiology_BodySite_VS</t>
+    <t>DICOM tagに設定されているコードをデフォルトとするが、JJ1017Pの小部位コードの利用を許容する。</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/body-site</t>
   </si>
   <si>
     <t>.targetSiteCode</t>
@@ -6501,9 +6504,11 @@
       <c r="X40" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="Y40" s="2"/>
+      <c r="Y40" t="s" s="2">
+        <v>377</v>
+      </c>
       <c r="Z40" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>79</v>
@@ -6539,10 +6544,10 @@
         <v>79</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>79</v>
@@ -6553,10 +6558,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6582,13 +6587,13 @@
         <v>171</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6617,10 +6622,10 @@
         <v>285</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>79</v>
@@ -6638,7 +6643,7 @@
         <v>79</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6656,10 +6661,10 @@
         <v>79</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>79</v>
@@ -6670,10 +6675,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6696,16 +6701,16 @@
         <v>91</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6755,7 +6760,7 @@
         <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6773,10 +6778,10 @@
         <v>79</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>79</v>
@@ -6787,10 +6792,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6816,13 +6821,13 @@
         <v>198</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6872,7 +6877,7 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -6893,7 +6898,7 @@
         <v>204</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>79</v>
@@ -6904,14 +6909,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6933,16 +6938,16 @@
         <v>316</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>79</v>
@@ -6991,7 +6996,7 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7006,13 +7011,13 @@
         <v>102</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>228</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>79</v>
@@ -7023,10 +7028,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7138,10 +7143,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7255,10 +7260,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7374,10 +7379,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7403,14 +7408,14 @@
         <v>263</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>79</v>
@@ -7435,13 +7440,13 @@
         <v>79</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>79</v>
@@ -7459,7 +7464,7 @@
         <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7491,10 +7496,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7517,16 +7522,16 @@
         <v>91</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7576,7 +7581,7 @@
         <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>90</v>
@@ -7594,24 +7599,24 @@
         <v>79</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7637,13 +7642,13 @@
         <v>316</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7693,7 +7698,7 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7711,7 +7716,7 @@
         <v>79</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>79</v>
@@ -7725,10 +7730,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7840,10 +7845,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7957,10 +7962,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8076,14 +8081,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8105,16 +8110,16 @@
         <v>92</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>79</v>
@@ -8127,7 +8132,7 @@
         <v>79</v>
       </c>
       <c r="T54" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="U54" t="s" s="2">
         <v>79</v>
@@ -8163,7 +8168,7 @@
         <v>79</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>90</v>
@@ -8184,7 +8189,7 @@
         <v>340</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>79</v>
@@ -8195,14 +8200,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8224,13 +8229,13 @@
         <v>171</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8256,11 +8261,11 @@
         <v>79</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Y55" s="2"/>
       <c r="Z55" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>79</v>
@@ -8278,7 +8283,7 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>90</v>
@@ -8296,10 +8301,10 @@
         <v>79</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>79</v>
@@ -8310,14 +8315,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8339,13 +8344,13 @@
         <v>240</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8395,7 +8400,7 @@
         <v>79</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8413,10 +8418,10 @@
         <v>79</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>79</v>
@@ -8427,10 +8432,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8456,13 +8461,13 @@
         <v>309</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8512,7 +8517,7 @@
         <v>79</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8530,10 +8535,10 @@
         <v>79</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>79</v>
